--- a/data/trans_bre/P23_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,46; -15,62</t>
+          <t>-25,57; -15,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -8,34</t>
+          <t>-19,01; -8,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,99; -6,46</t>
+          <t>-16,5; -7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -5,1</t>
+          <t>-14,39; -5,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,28; -37,99</t>
+          <t>-55,43; -38,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,44; -25,14</t>
+          <t>-47,77; -25,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,99; -19,05</t>
+          <t>-42,03; -20,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,83; -20,77</t>
+          <t>-46,91; -20,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,35; -12,68</t>
+          <t>-21,57; -13,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -5,22</t>
+          <t>-13,56; -5,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,85; -2,58</t>
+          <t>-10,65; -2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 8,82</t>
+          <t>-7,42; 9,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,9; -33,95</t>
+          <t>-50,8; -34,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,01; -14,8</t>
+          <t>-34,37; -14,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,16; -7,57</t>
+          <t>-30,94; -8,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 79,88</t>
+          <t>-29,28; 81,63</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -7,38</t>
+          <t>-17,1; -7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -3,53</t>
+          <t>-13,69; -3,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -6,87</t>
+          <t>-16,82; -7,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -4,88</t>
+          <t>-23,08; -5,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,93; -21,44</t>
+          <t>-43,8; -21,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,53; -10,11</t>
+          <t>-34,36; -10,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -17,89</t>
+          <t>-38,89; -18,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,45; -18,72</t>
+          <t>-71,92; -19,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -7,89</t>
+          <t>-16,11; -8,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -4,12</t>
+          <t>-12,85; -4,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -1,01</t>
+          <t>-9,61; -1,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -1,92</t>
+          <t>-10,77; -1,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,56; -20,99</t>
+          <t>-38,73; -20,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -11,86</t>
+          <t>-33,44; -12,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,75; -3,21</t>
+          <t>-29,72; -5,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,05; -9,37</t>
+          <t>-42,41; -9,06</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -12,85</t>
+          <t>-17,6; -13,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -7,45</t>
+          <t>-12,05; -7,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -6,3</t>
+          <t>-10,76; -6,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -1,16</t>
+          <t>-9,66; -1,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,77; -33,23</t>
+          <t>-42,63; -34,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,88; -21,0</t>
+          <t>-32,09; -21,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,76; -18,77</t>
+          <t>-30,1; -18,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,09; -8,97</t>
+          <t>-38,15; -7,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,93</t>
+          <t>-10,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-35,38%</t>
+          <t>-36,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,57; -15,51</t>
+          <t>-25,09; -15,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,01; -8,93</t>
+          <t>-18,56; -9,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,06</t>
+          <t>-17,09; -7,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -5,32</t>
+          <t>-14,77; -5,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,43; -38,28</t>
+          <t>-54,32; -37,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,77; -25,32</t>
+          <t>-47,23; -26,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -20,34</t>
+          <t>-43,39; -21,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,91; -20,56</t>
+          <t>-47,26; -22,81</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,86%</t>
+          <t>-24,85%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -13,02</t>
+          <t>-21,54; -13,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -5,07</t>
+          <t>-13,92; -5,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -2,65</t>
+          <t>-10,9; -2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 9,37</t>
+          <t>-9,68; -2,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,8; -34,26</t>
+          <t>-50,83; -35,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,37; -14,41</t>
+          <t>-34,91; -14,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -8,85</t>
+          <t>-31,22; -8,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 81,63</t>
+          <t>-36,52; -9,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-11,8</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-41,37%</t>
+          <t>-19,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,1; -7,4</t>
+          <t>-17,52; -7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -3,68</t>
+          <t>-13,8; -3,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -7,15</t>
+          <t>-17,1; -7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -5,09</t>
+          <t>-9,8; -0,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,8; -21,65</t>
+          <t>-44,75; -20,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,36; -10,3</t>
+          <t>-34,41; -10,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-38,89; -18,58</t>
+          <t>-39,77; -18,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,92; -19,73</t>
+          <t>-33,05; -3,29</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-5,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-24,54%</t>
+          <t>-23,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -8,0</t>
+          <t>-16,55; -7,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -4,13</t>
+          <t>-13,1; -4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,61; -1,62</t>
+          <t>-9,39; -1,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -1,98</t>
+          <t>-9,16; -2,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,73; -20,76</t>
+          <t>-39,72; -21,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,44; -12,5</t>
+          <t>-34,01; -13,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,72; -5,71</t>
+          <t>-29,46; -6,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -9,06</t>
+          <t>-34,82; -9,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-6,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,16%</t>
+          <t>-25,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -13,2</t>
+          <t>-17,47; -13,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -7,62</t>
+          <t>-12,24; -7,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -6,27</t>
+          <t>-10,92; -6,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,31</t>
+          <t>-8,61; -4,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -34,13</t>
+          <t>-42,89; -34,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,09; -21,53</t>
+          <t>-32,26; -21,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -18,97</t>
+          <t>-30,31; -19,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -7,79</t>
+          <t>-32,16; -18,44</t>
         </is>
       </c>
     </row>
